--- a/output/北塩原村_見込量算定_MECEチェック.xlsx
+++ b/output/北塩原村_見込量算定_MECEチェック.xlsx
@@ -820,7 +820,7 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>3　マニュアルが（参考）として示すアンケートによる増減判断（E-3）が未適用だった。第1次概算は令和8年9月24日、アンケート集計は10月2日であり、算定時点で材料がなかったためである。問27-1×問27-3で実施すると増加要素20・減少要素11（分母28人）で増加傾向を示し、全サービス据え置きという現在の置き方とは向きが異なる。</t>
+          <t>3　マニュアルが（参考）として示すアンケートによる増減判断（E-3）が未適用だった。第1次概算は令和8年9月24日、アンケート集計は10月2日であり、算定時点で材料がなかったためである。問27-1×問27-3で実施すると増加要素19・減少要素9（分母27人）で増加傾向を示し、全サービス据え置きという現在の置き方とは向きが異なる。</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>第1次概算は令和8年9月24日、アンケート集計は10月2日のため材料がなかった。問27-1×問27-3で判断すると増加要素20・減少要素11で増加傾向であり、全サービス据え置きという現在の置き方と向きが異なる</t>
+          <t>第1次概算は令和8年9月24日、アンケート集計は10月2日のため材料がなかった。問27-1×問27-3で判断すると増加要素19・減少要素9で増加傾向であり、全サービス据え置きという現在の置き方と向きが異なる</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>アンケートで「就労継続支援Ａ型を現在利用」2人・「就労選択支援を現在利用」2人の回答があることの確認</t>
+          <t>アンケートで「就労継続支援Ａ型を現在利用」1人・「就労選択支援を現在利用」1人の回答があることの確認</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>継続入所者の控除（E-1）が未確認。個室化等の見込み（E-6）は設定しない。アンケートは増加方向（現在6人・今後10人）で成果目標の削減方向と逆（08シート）</t>
+          <t>継続入所者の控除（E-1）が未確認。個室化等の見込み（E-6）は設定しない。アンケートは増加方向（現在5人・今後9人）で成果目標の削減方向と逆（08シート）</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>マニュアルは、実績値による見込量を算出した上で「現在のサービス利用」×「今後3年以内の利用希望」のクロスにより増加要素と減少要素を数え、見込量を検討する手順を示している。第1次概算の時点ではアンケートの集計が出ていなかったため未実施であった。障がい者版の問27-1×問27-3により実施した（分母：両設問に回答した28人／回答41人）。</t>
+          <t>マニュアルは、実績値による見込量を算出した上で「現在のサービス利用」×「今後3年以内の利用希望」のクロスにより増加要素と減少要素を数え、見込量を検討する手順を示している。第1次概算の時点ではアンケートの集計が出ていなかったため未実施であった。障がい者版の問27-1×問27-3により実施した（分母：両設問に回答した27人／回答38人）。</t>
         </is>
       </c>
     </row>
@@ -4763,13 +4763,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>1</v>
@@ -4874,13 +4874,13 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>2</v>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
@@ -5133,13 +5133,13 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>2</v>
@@ -5170,13 +5170,13 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>2</v>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>5</v>
@@ -5244,13 +5244,13 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="E18" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>2</v>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>1</v>
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0</v>
@@ -5355,13 +5355,13 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>■ 増加要素 20　減少要素 11　→ 増加傾向（マニュアルの判断方法による）</t>
+          <t>■ 増加要素 19　減少要素 9　→ 増加傾向（マニュアルの判断方法による）</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>1　分母が小さい。両設問に回答したのは28人で、手帳所持者154人の18％である。1人の回答が3.6ポイントに相当するため、増減の向きは参考にとどまる。</t>
+          <t>1　分母が小さい。両設問に回答したのは27人で、手帳所持者154人の18％である。1人の回答が3.6ポイントに相当するため、増減の向きは参考にとどまる。</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>3　自己申告であり給付実績と一致しない。就労継続支援Ａ型を「現在利用」2人、就労選択支援を「現在利用」2人の回答があるが、令和2〜7年度の給付実績にいずれも計上がない。他サービスとの混同の可能性を含め村に確認する（M-13）。</t>
+          <t>3　自己申告であり給付実績と一致しない。就労継続支援Ａ型を「現在利用」1人、就労選択支援を「現在利用」1人の回答があるが、令和2〜7年度の給付実績にいずれも計上がない。他サービスとの混同の可能性を含め村に確認する（M-13）。</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>5　施設入所支援は現在6人・今後10人で最も増加方向が強いが、別表第一 四は令和7年度末の施設入所者数の5％以上の削減を望ましいとしており、向きが逆である。入所希望を地域生活の選択肢で受け止める方策（共同生活援助・地域生活支援拠点等）と併せて整理する必要がある。</t>
+          <t>5　施設入所支援は現在5人・今後9人で最も増加方向が強いが、別表第一 四は令和7年度末の施設入所者数の5％以上の削減を望ましいとしており、向きが逆である。入所希望を地域生活の選択肢で受け止める方策（共同生活援助・地域生活支援拠点等）と併せて整理する必要がある。</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_見込量算定_MECEチェック.xlsx
+++ b/output/北塩原村_見込量算定_MECEチェック.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>村への照会に追加し（M-10）、該当者0であることを確認のうえ計画素案 第5章1に「継続入所者に該当する者はいない」旨を明記する</t>
+          <t>村への照会に追加し（Ｍ-10）、該当者0であることを確認のうえ計画素案 第5章1に「継続入所者に該当する者はいない」旨を明記する</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>村の保育所・認定こども園・放課後児童クラブにおける障がい児の受入人数と加配の状況を照会し（M-11）、第5章7の考え方欄に反映する</t>
+          <t>村の保育所・認定こども園・放課後児童クラブにおける障がい児の受入人数と加配の状況を照会し（Ｍ-11）、第5章7の考え方欄に反映する</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>村への照会に追加（M-9）</t>
+          <t>村への照会に追加（Ｍ-9）</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の村照会M-1〜M-8・県照会Q-1〜Q-3に続けて番号を付した。M-10・M-11は告示が「ものとする」とした要件に係るため最優先とする。</t>
+          <t>既存の村照会Ｍ-1〜Ｍ-8・県照会Q-1〜Q-3に続けて番号を付した。Ｍ-10・Ｍ-11は告示が「ものとする」とした要件に係るため最優先とする。</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>M-9</t>
+          <t>Ｍ-9</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>Ｍ-10</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Ｍ-11</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Ｍ-12</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>Ｍ-13</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>M-4・H-4</t>
+          <t>Ｍ-4・H-4</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>H-7・M-8で対象者の有無を照会中</t>
+          <t>H-7・Ｍ-8で対象者の有無を照会中</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>給付実績に計上がない（H-4・M-4）。アンケートで現在利用2人の回答がある</t>
+          <t>給付実績に計上がない（H-4・Ｍ-4）。アンケートで現在利用2人の回答がある</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>請求件数76件÷12は実利用者数と一致しない（X-7）。実人数はM-2で照会中</t>
+          <t>請求件数76件÷12は実利用者数と一致しない（X-7）。実人数はＭ-2で照会中</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>保育所等の受入体制を踏まえた設定（E-2）が未反映。急減の理由はM-1で照会中</t>
+          <t>保育所等の受入体制を踏まえた設定（E-2）が未反映。急減の理由はＭ-1で照会中</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>請求8件。実人数はM-2で照会中</t>
+          <t>請求8件。実人数はＭ-2で照会中</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>市町村の事項だが見込量算定ブックの系列にない（E-8）。令和8年8月19日改正で医療的ケア者（成人）が加わった（M-6）</t>
+          <t>市町村の事項だが見込量算定ブックの系列にない（E-8）。令和8年8月19日改正で医療的ケア者（成人）が加わった（Ｍ-6）</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>H-8として0で据え置き、M-5・M-6で村に照会中。09_重度障がい者の内数シートに枠を設けている</t>
+          <t>H-8として0で据え置き、Ｍ-5・Ｍ-6で村に照会中。09_重度障がい者の内数シートに枠を設けている</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>村への照会に「短期入所3件の福祉型・医療型の別」を追加する（新規・M-9）</t>
+          <t>村への照会に「短期入所3件の福祉型・医療型の別」を追加する（新規・Ｍ-9）</t>
         </is>
       </c>
     </row>
@@ -5448,14 +5448,14 @@
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>3　自己申告であり給付実績と一致しない。就労継続支援Ａ型を「現在利用」1人、就労選択支援を「現在利用」1人の回答があるが、令和2〜7年度の給付実績にいずれも計上がない。他サービスとの混同の可能性を含め村に確認する（M-13）。</t>
+          <t>3　自己申告であり給付実績と一致しない。就労継続支援Ａ型を「現在利用」1人、就労選択支援を「現在利用」1人の回答があるが、令和2〜7年度の給付実績にいずれも計上がない。他サービスとの混同の可能性を含め村に確認する（Ｍ-13）。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>4　障がい児版は回答3人のため、この手順は適用しない。児童発達支援の急減（M-1）は個人単位の移動であり、アンケートの増減判断では捉えられない。</t>
+          <t>4　障がい児版は回答3人のため、この手順は適用しない。児童発達支援の急減（Ｍ-1）は個人単位の移動であり、アンケートの増減判断では捉えられない。</t>
         </is>
       </c>
     </row>
